--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -33676,6 +33676,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="G1449" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -33699,6 +33699,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>1.62000000476837</v>
+      </c>
+      <c r="G1450" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -33722,6 +33722,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1451" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -33745,6 +33745,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="G1452" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -33586,22 +33586,22 @@
     </row>
     <row r="1445">
       <c r="A1445" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1445" t="n">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="C1445" t="n">
+        <v>1.72000002861023</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="F1445" t="n">
         <v>1.62999999523163</v>
-      </c>
-      <c r="D1445" t="n">
-        <v>1.5900000333786</v>
-      </c>
-      <c r="E1445" t="n">
-        <v>1.62999999523163</v>
-      </c>
-      <c r="F1445" t="n">
-        <v>1.5900000333786</v>
       </c>
       <c r="G1445" t="s">
         <v>7</v>
@@ -33609,22 +33609,22 @@
     </row>
     <row r="1446">
       <c r="A1446" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1446" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="C1446" t="n">
-        <v>1.61000001430511</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="D1446" t="n">
-        <v>1.55999994277954</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="E1446" t="n">
-        <v>1.61000001430511</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="F1446" t="n">
-        <v>1.55999994277954</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="G1446" t="s">
         <v>7</v>
@@ -33632,22 +33632,22 @@
     </row>
     <row r="1447">
       <c r="A1447" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1447" t="n">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="C1447" t="n">
-        <v>1.54999995231628</v>
+        <v>1.61000001430511</v>
       </c>
       <c r="D1447" t="n">
-        <v>1.51999998092651</v>
+        <v>1.55999994277954</v>
       </c>
       <c r="E1447" t="n">
-        <v>1.52999997138977</v>
+        <v>1.61000001430511</v>
       </c>
       <c r="F1447" t="n">
-        <v>1.52999997138977</v>
+        <v>1.55999994277954</v>
       </c>
       <c r="G1447" t="s">
         <v>7</v>
@@ -33655,22 +33655,22 @@
     </row>
     <row r="1448">
       <c r="A1448" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1448" t="n">
-        <v>26500</v>
+        <v>6000</v>
       </c>
       <c r="C1448" t="n">
-        <v>1.6599999666214</v>
+        <v>1.54999995231628</v>
       </c>
       <c r="D1448" t="n">
-        <v>1.53999996185303</v>
+        <v>1.51999998092651</v>
       </c>
       <c r="E1448" t="n">
-        <v>1.53999996185303</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="F1448" t="n">
-        <v>1.58000004291534</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="G1448" t="s">
         <v>7</v>
@@ -33678,13 +33678,13 @@
     </row>
     <row r="1449">
       <c r="A1449" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1449" t="n">
-        <v>12000</v>
+        <v>26500</v>
       </c>
       <c r="C1449" t="n">
-        <v>1.62999999523163</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="D1449" t="n">
         <v>1.53999996185303</v>
@@ -33693,7 +33693,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="F1449" t="n">
-        <v>1.5900000333786</v>
+        <v>1.58000004291534</v>
       </c>
       <c r="G1449" t="s">
         <v>7</v>
@@ -33701,22 +33701,22 @@
     </row>
     <row r="1450">
       <c r="A1450" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1450" t="n">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="C1450" t="n">
-        <v>1.6599999666214</v>
+        <v>1.62999999523163</v>
       </c>
       <c r="D1450" t="n">
-        <v>1.61000001430511</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="E1450" t="n">
-        <v>1.61000001430511</v>
+        <v>1.53999996185303</v>
       </c>
       <c r="F1450" t="n">
-        <v>1.62000000476837</v>
+        <v>1.5900000333786</v>
       </c>
       <c r="G1450" t="s">
         <v>7</v>
@@ -33724,22 +33724,22 @@
     </row>
     <row r="1451">
       <c r="A1451" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1451" t="n">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="C1451" t="n">
-        <v>1.70000004768372</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="D1451" t="n">
-        <v>1.64999997615814</v>
+        <v>1.61000001430511</v>
       </c>
       <c r="E1451" t="n">
-        <v>1.64999997615814</v>
+        <v>1.61000001430511</v>
       </c>
       <c r="F1451" t="n">
-        <v>1.6599999666214</v>
+        <v>1.62000000476837</v>
       </c>
       <c r="G1451" t="s">
         <v>7</v>
@@ -33747,22 +33747,22 @@
     </row>
     <row r="1452">
       <c r="A1452" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1452" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="C1452" t="n">
-        <v>1.67999994754791</v>
+        <v>1.70000004768372</v>
       </c>
       <c r="D1452" t="n">
-        <v>1.60000002384186</v>
+        <v>1.64999997615814</v>
       </c>
       <c r="E1452" t="n">
-        <v>1.67999994754791</v>
+        <v>1.64999997615814</v>
       </c>
       <c r="F1452" t="n">
-        <v>1.61000001430511</v>
+        <v>1.6599999666214</v>
       </c>
       <c r="G1452" t="s">
         <v>7</v>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -38205,6 +38205,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1456">
+      <c r="A1456" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1456" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="D1456" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G1456" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -38231,6 +38231,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>5500</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -603,7 +603,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717635154724</v>
+        <v>2.80717658996582</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776389122009</v>
+        <v>3.22776412963867</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.16907739639282</v>
+        <v>3.1690776348114</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294810295105</v>
+        <v>3.44294834136963</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229146957397</v>
+        <v>3.47229170799255</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557535171509</v>
+        <v>3.32557511329651</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74848985671997</v>
+        <v>2.74849009513855</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834031105042</v>
+        <v>2.30834007263184</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440027236938</v>
+        <v>2.48440003395081</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016078472137</v>
+        <v>1.78016090393066</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395127773285</v>
+        <v>1.16395139694214</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329452514648</v>
+        <v>1.19329464435577</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.60410094261169</v>
+        <v>1.6041008234024</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475769519806</v>
+        <v>1.57475757598877</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.58453869819641</v>
+        <v>1.5845388174057</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388194561005</v>
+        <v>1.61388206481934</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -38254,6 +38254,32 @@
         <v>1.67999994754791</v>
       </c>
       <c r="H1457" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="H1458" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -603,7 +603,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717658996582</v>
+        <v>2.80717635154724</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776412963867</v>
+        <v>3.22776389122009</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.1690776348114</v>
+        <v>3.16907739639282</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294834136963</v>
+        <v>3.44294810295105</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229170799255</v>
+        <v>3.47229146957397</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557511329651</v>
+        <v>3.32557535171509</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74849009513855</v>
+        <v>2.74848985671997</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834007263184</v>
+        <v>2.30834031105042</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440003395081</v>
+        <v>2.48440027236938</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016090393066</v>
+        <v>1.78016078472137</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395139694214</v>
+        <v>1.16395127773285</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329464435577</v>
+        <v>1.19329452514648</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.6041008234024</v>
+        <v>1.60410094261169</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475757598877</v>
+        <v>1.57475769519806</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.5845388174057</v>
+        <v>1.58453869819641</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388206481934</v>
+        <v>1.61388194561005</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -38280,6 +38280,32 @@
         <v>1.66999995708466</v>
       </c>
       <c r="H1458" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>1.66999995708466</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>1.64999997615814</v>
+      </c>
+      <c r="H1459" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -603,7 +603,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717635154724</v>
+        <v>2.80717658996582</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776389122009</v>
+        <v>3.22776412963867</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.16907739639282</v>
+        <v>3.1690776348114</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294810295105</v>
+        <v>3.44294834136963</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229146957397</v>
+        <v>3.47229170799255</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557535171509</v>
+        <v>3.32557511329651</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74848985671997</v>
+        <v>2.74849009513855</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834031105042</v>
+        <v>2.30834007263184</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440027236938</v>
+        <v>2.48440003395081</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016078472137</v>
+        <v>1.78016090393066</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395127773285</v>
+        <v>1.16395139694214</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329452514648</v>
+        <v>1.19329464435577</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.60410094261169</v>
+        <v>1.6041008234024</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475769519806</v>
+        <v>1.57475757598877</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.58453869819641</v>
+        <v>1.5845388174057</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388194561005</v>
+        <v>1.61388206481934</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -38358,6 +38358,32 @@
         <v>1.62999999523163</v>
       </c>
       <c r="H1461" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>10500</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1462" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -34060,7 +34060,9 @@
       <c r="E1465" t="n">
         <v>1.61000001430511</v>
       </c>
-      <c r="F1465"/>
+      <c r="F1465" t="n">
+        <v>1.6599999666214</v>
+      </c>
       <c r="G1465" t="s">
         <v>7</v>
       </c>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -34067,6 +34067,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1466">
+      <c r="A1466" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="G1466" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="F1467"/>
+      <c r="G1467" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -34106,8 +34106,31 @@
       <c r="E1467" t="n">
         <v>1.6599999666214</v>
       </c>
-      <c r="F1467"/>
+      <c r="F1467" t="n">
+        <v>1.60000002384186</v>
+      </c>
       <c r="G1467" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="F1468"/>
+      <c r="G1468" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -34129,8 +34129,31 @@
       <c r="E1468" t="n">
         <v>1.5900000333786</v>
       </c>
-      <c r="F1468"/>
+      <c r="F1468" t="n">
+        <v>1.60000002384186</v>
+      </c>
       <c r="G1468" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1469" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="D1469" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F1469"/>
+      <c r="G1469" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -34159,6 +34159,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1470">
+      <c r="A1470" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1470" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1470" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -38647,6 +38647,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>1.62999999523163</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1473" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1473" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -603,7 +603,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717635154724</v>
+        <v>2.80717658996582</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776389122009</v>
+        <v>3.22776412963867</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.16907739639282</v>
+        <v>3.1690776348114</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294810295105</v>
+        <v>3.44294834136963</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229146957397</v>
+        <v>3.47229170799255</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557535171509</v>
+        <v>3.32557511329651</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74848985671997</v>
+        <v>2.74849009513855</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834031105042</v>
+        <v>2.30834007263184</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440027236938</v>
+        <v>2.48440003395081</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016078472137</v>
+        <v>1.78016090393066</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395127773285</v>
+        <v>1.16395139694214</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329452514648</v>
+        <v>1.19329464435577</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.60410094261169</v>
+        <v>1.6041008234024</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475769519806</v>
+        <v>1.57475757598877</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.58453869819641</v>
+        <v>1.5845388174057</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388194561005</v>
+        <v>1.61388206481934</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -38670,6 +38670,32 @@
         <v>1.63999998569489</v>
       </c>
       <c r="H1473" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G1474" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="H1474" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -43153,6 +43153,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1476">
+      <c r="A1476" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>1.51999998092651</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="G1476" t="n">
+        <v>1.57000005245209</v>
+      </c>
+      <c r="H1476" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H12" t="n">
         <v>16000</v>
@@ -775,7 +775,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H14" t="n">
         <v>30000</v>
@@ -804,7 +804,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H15" t="n">
         <v>11000</v>
@@ -949,7 +949,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717658996582</v>
+        <v>2.80717635154724</v>
       </c>
       <c r="H20" t="n">
         <v>19000</v>
@@ -1007,7 +1007,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H22" t="n">
         <v>3000</v>
@@ -1065,7 +1065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H24" t="n">
         <v>33000</v>
@@ -1094,7 +1094,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H25" t="n">
         <v>20000</v>
@@ -1210,7 +1210,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H29" t="n">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1326,7 +1326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1471,7 +1471,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H38" t="n">
         <v>3000</v>
@@ -1500,7 +1500,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H39" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H46" t="n">
         <v>13000</v>
@@ -2225,7 +2225,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H64" t="n">
         <v>35000</v>
@@ -2312,7 +2312,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H67" t="n">
         <v>83000</v>
@@ -2370,7 +2370,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2486,7 +2486,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H73" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H77" t="n">
         <v>1000</v>
@@ -2631,7 +2631,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H79" t="n">
         <v>4000</v>
@@ -2863,7 +2863,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2950,7 +2950,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H95" t="n">
         <v>15000</v>
@@ -3153,7 +3153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H100" t="n">
         <v>58000</v>
@@ -3327,7 +3327,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H102" t="n">
         <v>31000</v>
@@ -3385,7 +3385,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H104" t="n">
         <v>7000</v>
@@ -3414,7 +3414,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H105" t="n">
         <v>47000</v>
@@ -3501,7 +3501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H108" t="n">
         <v>46000</v>
@@ -3762,7 +3762,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H117" t="n">
         <v>2000</v>
@@ -3791,7 +3791,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H118" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -3907,7 +3907,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H122" t="n">
         <v>11000</v>
@@ -3936,7 +3936,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H123" t="n">
         <v>12000</v>
@@ -3994,7 +3994,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H125" t="n">
         <v>6500</v>
@@ -4081,7 +4081,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H128" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H139" t="n">
         <v>6500</v>
@@ -4429,7 +4429,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4458,7 +4458,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H141" t="n">
         <v>16500</v>
@@ -4545,7 +4545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H147" t="n">
         <v>2500</v>
@@ -4661,7 +4661,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H148" t="n">
         <v>1500</v>
@@ -4690,7 +4690,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H149" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H152" t="n">
         <v>6500</v>
@@ -4806,7 +4806,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H153" t="n">
         <v>3500</v>
@@ -4835,7 +4835,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H160" t="n">
         <v>2500</v>
@@ -5038,7 +5038,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H161" t="n">
         <v>2000</v>
@@ -5067,7 +5067,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H163" t="n">
         <v>1500</v>
@@ -5125,7 +5125,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5154,7 +5154,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H174" t="n">
         <v>119000</v>
@@ -5473,7 +5473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H176" t="n">
         <v>17500</v>
@@ -5705,7 +5705,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H184" t="n">
         <v>11000</v>
@@ -5734,7 +5734,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H191" t="n">
         <v>45000</v>
@@ -5937,7 +5937,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H192" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776412963867</v>
+        <v>3.22776389122009</v>
       </c>
       <c r="H198" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.1690776348114</v>
+        <v>3.16907739639282</v>
       </c>
       <c r="H203" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H205" t="n">
         <v>5500</v>
@@ -6372,7 +6372,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H207" t="n">
         <v>7000</v>
@@ -6401,7 +6401,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H208" t="n">
         <v>12500</v>
@@ -6430,7 +6430,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H209" t="n">
         <v>2500</v>
@@ -6546,7 +6546,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H213" t="n">
         <v>7000</v>
@@ -6575,7 +6575,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H214" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H216" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H219" t="n">
         <v>14000</v>
@@ -6749,7 +6749,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294834136963</v>
+        <v>3.44294810295105</v>
       </c>
       <c r="H220" t="n">
         <v>209000</v>
@@ -6778,7 +6778,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229170799255</v>
+        <v>3.47229146957397</v>
       </c>
       <c r="H221" t="n">
         <v>221000</v>
@@ -6807,7 +6807,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H222" t="n">
         <v>65000</v>
@@ -7039,7 +7039,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H230" t="n">
         <v>25000</v>
@@ -7097,7 +7097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H233" t="n">
         <v>18000</v>
@@ -7155,7 +7155,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H234" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557511329651</v>
+        <v>3.32557535171509</v>
       </c>
       <c r="H238" t="n">
         <v>8500</v>
@@ -7300,7 +7300,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7445,7 +7445,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7561,7 +7561,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H248" t="n">
         <v>11500</v>
@@ -7648,7 +7648,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H251" t="n">
         <v>25500</v>
@@ -7735,7 +7735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H254" t="n">
         <v>18000</v>
@@ -7764,7 +7764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H256" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H262" t="n">
         <v>11500</v>
@@ -7996,7 +7996,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H263" t="n">
         <v>11500</v>
@@ -8083,7 +8083,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H266" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H275" t="n">
         <v>2500</v>
@@ -8373,7 +8373,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H277" t="n">
         <v>500</v>
@@ -8431,7 +8431,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H284" t="n">
         <v>1500</v>
@@ -8634,7 +8634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H285" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H291" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H298" t="n">
         <v>8500</v>
@@ -9040,7 +9040,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H299" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9330,7 +9330,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9417,7 +9417,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H313" t="n">
         <v>5500</v>
@@ -9475,7 +9475,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H314" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H317" t="n">
         <v>14500</v>
@@ -9591,7 +9591,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H320" t="n">
         <v>2000</v>
@@ -9736,7 +9736,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H323" t="n">
         <v>500</v>
@@ -9765,7 +9765,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H344" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H345" t="n">
         <v>8000</v>
@@ -10461,7 +10461,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -11041,7 +11041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H368" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H369" t="n">
         <v>10000</v>
@@ -11099,7 +11099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H370" t="n">
         <v>5000</v>
@@ -11157,7 +11157,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H372" t="n">
         <v>2500</v>
@@ -11186,7 +11186,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H376" t="n">
         <v>4000</v>
@@ -11302,7 +11302,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H383" t="n">
         <v>1000</v>
@@ -11505,7 +11505,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H385" t="n">
         <v>2000</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74849009513855</v>
+        <v>2.74848985671997</v>
       </c>
       <c r="H390" t="n">
         <v>40500</v>
@@ -11882,7 +11882,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H397" t="n">
         <v>2500</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H425" t="n">
         <v>1000</v>
@@ -12723,7 +12723,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H442" t="n">
         <v>500</v>
@@ -13216,7 +13216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H450" t="n">
         <v>5000</v>
@@ -13448,7 +13448,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H458" t="n">
         <v>2000</v>
@@ -13680,7 +13680,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834007263184</v>
+        <v>2.30834031105042</v>
       </c>
       <c r="H459" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H471" t="n">
         <v>5500</v>
@@ -14057,7 +14057,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440003395081</v>
+        <v>2.48440027236938</v>
       </c>
       <c r="H485" t="n">
         <v>3000</v>
@@ -14724,7 +14724,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H519" t="n">
         <v>2000</v>
@@ -15536,7 +15536,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H523" t="n">
         <v>1500</v>
@@ -15565,7 +15565,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H535" t="n">
         <v>56000</v>
@@ -15942,7 +15942,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H537" t="n">
         <v>11000</v>
@@ -16000,7 +16000,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H539" t="n">
         <v>18500</v>
@@ -16058,7 +16058,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H541" t="n">
         <v>5500</v>
@@ -16087,7 +16087,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H545" t="n">
         <v>4000</v>
@@ -16377,7 +16377,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16667,7 +16667,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16812,7 +16812,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H568" t="n">
         <v>2500</v>
@@ -16870,7 +16870,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H569" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H573" t="n">
         <v>12000</v>
@@ -17218,7 +17218,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H581" t="n">
         <v>500</v>
@@ -17305,7 +17305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H584" t="n">
         <v>2000</v>
@@ -17334,7 +17334,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H588" t="n">
         <v>2500</v>
@@ -17450,7 +17450,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H591" t="n">
         <v>1000</v>
@@ -17537,7 +17537,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H603" t="n">
         <v>1000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H604" t="n">
         <v>3500</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H607" t="n">
         <v>2500</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H611" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H612" t="n">
         <v>2000</v>
@@ -18146,7 +18146,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H616" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H617" t="n">
         <v>500</v>
@@ -18378,7 +18378,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016090393066</v>
+        <v>1.78016078472137</v>
       </c>
       <c r="H621" t="n">
         <v>32500</v>
@@ -18465,7 +18465,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H624" t="n">
         <v>11000</v>
@@ -18552,7 +18552,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H627" t="n">
         <v>6500</v>
@@ -18581,7 +18581,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H628" t="n">
         <v>10000</v>
@@ -18755,7 +18755,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H634" t="n">
         <v>2500</v>
@@ -18784,7 +18784,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H655" t="n">
         <v>17000</v>
@@ -19393,7 +19393,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H656" t="n">
         <v>20000</v>
@@ -19422,7 +19422,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H660" t="n">
         <v>32000</v>
@@ -19538,7 +19538,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H661" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19712,7 +19712,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H667" t="n">
         <v>2000</v>
@@ -19741,7 +19741,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H672" t="n">
         <v>500</v>
@@ -19915,7 +19915,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H674" t="n">
         <v>4000</v>
@@ -20176,7 +20176,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20379,7 +20379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H690" t="n">
         <v>13500</v>
@@ -20408,7 +20408,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H701" t="n">
         <v>7000</v>
@@ -20756,7 +20756,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H703" t="n">
         <v>500</v>
@@ -20843,7 +20843,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20959,7 +20959,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H710" t="n">
         <v>1000</v>
@@ -21017,7 +21017,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H712" t="n">
         <v>3500</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H716" t="n">
         <v>500</v>
@@ -21220,7 +21220,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H719" t="n">
         <v>6500</v>
@@ -21249,7 +21249,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H722" t="n">
         <v>5500</v>
@@ -21336,7 +21336,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H723" t="n">
         <v>9500</v>
@@ -21655,7 +21655,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395139694214</v>
+        <v>1.16395127773285</v>
       </c>
       <c r="H734" t="n">
         <v>68000</v>
@@ -21742,7 +21742,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H737" t="n">
         <v>54000</v>
@@ -21800,7 +21800,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H739" t="n">
         <v>56500</v>
@@ -21829,7 +21829,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329464435577</v>
+        <v>1.19329452514648</v>
       </c>
       <c r="H740" t="n">
         <v>95000</v>
@@ -21916,7 +21916,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H743" t="n">
         <v>31000</v>
@@ -21945,7 +21945,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H744" t="n">
         <v>20000</v>
@@ -21974,7 +21974,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22177,7 +22177,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H752" t="n">
         <v>18500</v>
@@ -22554,7 +22554,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H765" t="n">
         <v>24000</v>
@@ -22612,7 +22612,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H767" t="n">
         <v>7500</v>
@@ -22670,7 +22670,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H769" t="n">
         <v>4000</v>
@@ -22699,7 +22699,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H770" t="n">
         <v>8000</v>
@@ -23047,7 +23047,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.6041008234024</v>
+        <v>1.60410094261169</v>
       </c>
       <c r="H782" t="n">
         <v>108000</v>
@@ -23105,7 +23105,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H784" t="n">
         <v>9500</v>
@@ -23163,7 +23163,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H786" t="n">
         <v>8500</v>
@@ -23192,7 +23192,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H787" t="n">
         <v>10500</v>
@@ -23221,7 +23221,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H788" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H790" t="n">
         <v>3500</v>
@@ -23308,7 +23308,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H791" t="n">
         <v>5000</v>
@@ -23337,7 +23337,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H792" t="n">
         <v>11500</v>
@@ -23395,7 +23395,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H794" t="n">
         <v>11000</v>
@@ -23424,7 +23424,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H799" t="n">
         <v>9000</v>
@@ -23569,7 +23569,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H800" t="n">
         <v>1500</v>
@@ -23598,7 +23598,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H801" t="n">
         <v>6000</v>
@@ -23627,7 +23627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H802" t="n">
         <v>15000</v>
@@ -23685,7 +23685,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23714,7 +23714,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H805" t="n">
         <v>5500</v>
@@ -23743,7 +23743,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H806" t="n">
         <v>7500</v>
@@ -23772,7 +23772,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H807" t="n">
         <v>12000</v>
@@ -23801,7 +23801,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H808" t="n">
         <v>5500</v>
@@ -23830,7 +23830,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H810" t="n">
         <v>2500</v>
@@ -23917,7 +23917,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H812" t="n">
         <v>9500</v>
@@ -24091,7 +24091,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H818" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H822" t="n">
         <v>1500</v>
@@ -24236,7 +24236,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H823" t="n">
         <v>500</v>
@@ -24265,7 +24265,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24381,7 +24381,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H828" t="n">
         <v>6000</v>
@@ -24439,7 +24439,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H830" t="n">
         <v>4000</v>
@@ -24584,7 +24584,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475757598877</v>
+        <v>1.57475769519806</v>
       </c>
       <c r="H835" t="n">
         <v>21000</v>
@@ -24613,7 +24613,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.5845388174057</v>
+        <v>1.58453869819641</v>
       </c>
       <c r="H836" t="n">
         <v>4500</v>
@@ -24903,7 +24903,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H846" t="n">
         <v>14000</v>
@@ -24932,7 +24932,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H851" t="n">
         <v>17500</v>
@@ -25077,7 +25077,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H852" t="n">
         <v>92500</v>
@@ -25135,7 +25135,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388206481934</v>
+        <v>1.61388194561005</v>
       </c>
       <c r="H854" t="n">
         <v>9000</v>
@@ -25193,7 +25193,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H856" t="n">
         <v>34000</v>
@@ -25309,7 +25309,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H860" t="n">
         <v>11000</v>
@@ -43179,6 +43179,35 @@
         <v>3500</v>
       </c>
       <c r="I1476" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1477" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D1477" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="G1477" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="H1477" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I1477" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -43211,6 +43211,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1478">
+      <c r="A1478" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1478" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D1478" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="G1478" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="H1478" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -43225,7 +43225,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="E1478" t="n">
-        <v>1.53999996185303</v>
+        <v>1.52999997138977</v>
       </c>
       <c r="F1478" t="n">
         <v>1.53999996185303</v>
@@ -43237,6 +43237,35 @@
         <v>6000</v>
       </c>
       <c r="I1478" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1.46000003814697</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H1479" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I1479" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H12" t="n">
         <v>16000</v>
@@ -775,7 +775,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H14" t="n">
         <v>30000</v>
@@ -804,7 +804,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H15" t="n">
         <v>11000</v>
@@ -949,7 +949,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717635154724</v>
+        <v>2.80717658996582</v>
       </c>
       <c r="H20" t="n">
         <v>19000</v>
@@ -1007,7 +1007,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H22" t="n">
         <v>3000</v>
@@ -1065,7 +1065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H24" t="n">
         <v>33000</v>
@@ -1094,7 +1094,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H25" t="n">
         <v>20000</v>
@@ -1210,7 +1210,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H29" t="n">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1326,7 +1326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1471,7 +1471,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H38" t="n">
         <v>3000</v>
@@ -1500,7 +1500,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H39" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H46" t="n">
         <v>13000</v>
@@ -2225,7 +2225,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H64" t="n">
         <v>35000</v>
@@ -2312,7 +2312,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H67" t="n">
         <v>83000</v>
@@ -2370,7 +2370,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2486,7 +2486,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H73" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H77" t="n">
         <v>1000</v>
@@ -2631,7 +2631,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H79" t="n">
         <v>4000</v>
@@ -2863,7 +2863,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2950,7 +2950,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H95" t="n">
         <v>15000</v>
@@ -3153,7 +3153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H100" t="n">
         <v>58000</v>
@@ -3327,7 +3327,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H102" t="n">
         <v>31000</v>
@@ -3385,7 +3385,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H104" t="n">
         <v>7000</v>
@@ -3414,7 +3414,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H105" t="n">
         <v>47000</v>
@@ -3501,7 +3501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H108" t="n">
         <v>46000</v>
@@ -3762,7 +3762,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H117" t="n">
         <v>2000</v>
@@ -3791,7 +3791,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H118" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -3907,7 +3907,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H122" t="n">
         <v>11000</v>
@@ -3936,7 +3936,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H123" t="n">
         <v>12000</v>
@@ -3994,7 +3994,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H125" t="n">
         <v>6500</v>
@@ -4081,7 +4081,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H128" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H139" t="n">
         <v>6500</v>
@@ -4429,7 +4429,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4458,7 +4458,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H141" t="n">
         <v>16500</v>
@@ -4545,7 +4545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H147" t="n">
         <v>2500</v>
@@ -4661,7 +4661,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H148" t="n">
         <v>1500</v>
@@ -4690,7 +4690,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H149" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H152" t="n">
         <v>6500</v>
@@ -4806,7 +4806,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H153" t="n">
         <v>3500</v>
@@ -4835,7 +4835,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H160" t="n">
         <v>2500</v>
@@ -5038,7 +5038,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H161" t="n">
         <v>2000</v>
@@ -5067,7 +5067,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H163" t="n">
         <v>1500</v>
@@ -5125,7 +5125,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5154,7 +5154,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H174" t="n">
         <v>119000</v>
@@ -5473,7 +5473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H176" t="n">
         <v>17500</v>
@@ -5705,7 +5705,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H184" t="n">
         <v>11000</v>
@@ -5734,7 +5734,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H191" t="n">
         <v>45000</v>
@@ -5937,7 +5937,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H192" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776389122009</v>
+        <v>3.22776412963867</v>
       </c>
       <c r="H198" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.16907739639282</v>
+        <v>3.1690776348114</v>
       </c>
       <c r="H203" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H205" t="n">
         <v>5500</v>
@@ -6372,7 +6372,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H207" t="n">
         <v>7000</v>
@@ -6401,7 +6401,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H208" t="n">
         <v>12500</v>
@@ -6430,7 +6430,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H209" t="n">
         <v>2500</v>
@@ -6546,7 +6546,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H213" t="n">
         <v>7000</v>
@@ -6575,7 +6575,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H214" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H216" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H219" t="n">
         <v>14000</v>
@@ -6749,7 +6749,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294810295105</v>
+        <v>3.44294834136963</v>
       </c>
       <c r="H220" t="n">
         <v>209000</v>
@@ -6778,7 +6778,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229146957397</v>
+        <v>3.47229170799255</v>
       </c>
       <c r="H221" t="n">
         <v>221000</v>
@@ -6807,7 +6807,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H222" t="n">
         <v>65000</v>
@@ -7039,7 +7039,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H230" t="n">
         <v>25000</v>
@@ -7097,7 +7097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H233" t="n">
         <v>18000</v>
@@ -7155,7 +7155,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H234" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557535171509</v>
+        <v>3.32557511329651</v>
       </c>
       <c r="H238" t="n">
         <v>8500</v>
@@ -7300,7 +7300,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7445,7 +7445,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7561,7 +7561,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H248" t="n">
         <v>11500</v>
@@ -7648,7 +7648,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H251" t="n">
         <v>25500</v>
@@ -7735,7 +7735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H254" t="n">
         <v>18000</v>
@@ -7764,7 +7764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H256" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H262" t="n">
         <v>11500</v>
@@ -7996,7 +7996,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H263" t="n">
         <v>11500</v>
@@ -8083,7 +8083,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H266" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H275" t="n">
         <v>2500</v>
@@ -8373,7 +8373,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H277" t="n">
         <v>500</v>
@@ -8431,7 +8431,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H284" t="n">
         <v>1500</v>
@@ -8634,7 +8634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H285" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H291" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H298" t="n">
         <v>8500</v>
@@ -9040,7 +9040,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H299" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9330,7 +9330,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9417,7 +9417,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H313" t="n">
         <v>5500</v>
@@ -9475,7 +9475,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H314" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H317" t="n">
         <v>14500</v>
@@ -9591,7 +9591,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H320" t="n">
         <v>2000</v>
@@ -9736,7 +9736,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H323" t="n">
         <v>500</v>
@@ -9765,7 +9765,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H344" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H345" t="n">
         <v>8000</v>
@@ -10461,7 +10461,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -11041,7 +11041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H368" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H369" t="n">
         <v>10000</v>
@@ -11099,7 +11099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H370" t="n">
         <v>5000</v>
@@ -11157,7 +11157,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H372" t="n">
         <v>2500</v>
@@ -11186,7 +11186,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H376" t="n">
         <v>4000</v>
@@ -11302,7 +11302,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H383" t="n">
         <v>1000</v>
@@ -11505,7 +11505,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H385" t="n">
         <v>2000</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74848985671997</v>
+        <v>2.74849009513855</v>
       </c>
       <c r="H390" t="n">
         <v>40500</v>
@@ -11882,7 +11882,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H397" t="n">
         <v>2500</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H425" t="n">
         <v>1000</v>
@@ -12723,7 +12723,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H442" t="n">
         <v>500</v>
@@ -13216,7 +13216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H450" t="n">
         <v>5000</v>
@@ -13448,7 +13448,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H458" t="n">
         <v>2000</v>
@@ -13680,7 +13680,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834031105042</v>
+        <v>2.30834007263184</v>
       </c>
       <c r="H459" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H471" t="n">
         <v>5500</v>
@@ -14057,7 +14057,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440027236938</v>
+        <v>2.48440003395081</v>
       </c>
       <c r="H485" t="n">
         <v>3000</v>
@@ -14724,7 +14724,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H519" t="n">
         <v>2000</v>
@@ -15536,7 +15536,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H523" t="n">
         <v>1500</v>
@@ -15565,7 +15565,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H535" t="n">
         <v>56000</v>
@@ -15942,7 +15942,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H537" t="n">
         <v>11000</v>
@@ -16000,7 +16000,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H539" t="n">
         <v>18500</v>
@@ -16058,7 +16058,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H541" t="n">
         <v>5500</v>
@@ -16087,7 +16087,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H545" t="n">
         <v>4000</v>
@@ -16377,7 +16377,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16667,7 +16667,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16812,7 +16812,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H568" t="n">
         <v>2500</v>
@@ -16870,7 +16870,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H569" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H573" t="n">
         <v>12000</v>
@@ -17218,7 +17218,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H581" t="n">
         <v>500</v>
@@ -17305,7 +17305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H584" t="n">
         <v>2000</v>
@@ -17334,7 +17334,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H588" t="n">
         <v>2500</v>
@@ -17450,7 +17450,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H591" t="n">
         <v>1000</v>
@@ -17537,7 +17537,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H603" t="n">
         <v>1000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H604" t="n">
         <v>3500</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H607" t="n">
         <v>2500</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H611" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H612" t="n">
         <v>2000</v>
@@ -18146,7 +18146,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H616" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H617" t="n">
         <v>500</v>
@@ -18378,7 +18378,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016078472137</v>
+        <v>1.78016090393066</v>
       </c>
       <c r="H621" t="n">
         <v>32500</v>
@@ -18465,7 +18465,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H624" t="n">
         <v>11000</v>
@@ -18552,7 +18552,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H627" t="n">
         <v>6500</v>
@@ -18581,7 +18581,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H628" t="n">
         <v>10000</v>
@@ -18755,7 +18755,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H634" t="n">
         <v>2500</v>
@@ -18784,7 +18784,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H655" t="n">
         <v>17000</v>
@@ -19393,7 +19393,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H656" t="n">
         <v>20000</v>
@@ -19422,7 +19422,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H660" t="n">
         <v>32000</v>
@@ -19538,7 +19538,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H661" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19712,7 +19712,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H667" t="n">
         <v>2000</v>
@@ -19741,7 +19741,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H672" t="n">
         <v>500</v>
@@ -19915,7 +19915,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H674" t="n">
         <v>4000</v>
@@ -20176,7 +20176,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20379,7 +20379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H690" t="n">
         <v>13500</v>
@@ -20408,7 +20408,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H701" t="n">
         <v>7000</v>
@@ -20756,7 +20756,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H703" t="n">
         <v>500</v>
@@ -20843,7 +20843,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20959,7 +20959,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H710" t="n">
         <v>1000</v>
@@ -21017,7 +21017,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H712" t="n">
         <v>3500</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H716" t="n">
         <v>500</v>
@@ -21220,7 +21220,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H719" t="n">
         <v>6500</v>
@@ -21249,7 +21249,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H722" t="n">
         <v>5500</v>
@@ -21336,7 +21336,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H723" t="n">
         <v>9500</v>
@@ -21655,7 +21655,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395127773285</v>
+        <v>1.16395139694214</v>
       </c>
       <c r="H734" t="n">
         <v>68000</v>
@@ -21742,7 +21742,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H737" t="n">
         <v>54000</v>
@@ -21800,7 +21800,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H739" t="n">
         <v>56500</v>
@@ -21829,7 +21829,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329452514648</v>
+        <v>1.19329464435577</v>
       </c>
       <c r="H740" t="n">
         <v>95000</v>
@@ -21916,7 +21916,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H743" t="n">
         <v>31000</v>
@@ -21945,7 +21945,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H744" t="n">
         <v>20000</v>
@@ -21974,7 +21974,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22177,7 +22177,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H752" t="n">
         <v>18500</v>
@@ -22554,7 +22554,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H765" t="n">
         <v>24000</v>
@@ -22612,7 +22612,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H767" t="n">
         <v>7500</v>
@@ -22670,7 +22670,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H769" t="n">
         <v>4000</v>
@@ -22699,7 +22699,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H770" t="n">
         <v>8000</v>
@@ -23047,7 +23047,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.60410094261169</v>
+        <v>1.6041008234024</v>
       </c>
       <c r="H782" t="n">
         <v>108000</v>
@@ -23105,7 +23105,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H784" t="n">
         <v>9500</v>
@@ -23163,7 +23163,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H786" t="n">
         <v>8500</v>
@@ -23192,7 +23192,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H787" t="n">
         <v>10500</v>
@@ -23221,7 +23221,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H788" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H790" t="n">
         <v>3500</v>
@@ -23308,7 +23308,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H791" t="n">
         <v>5000</v>
@@ -23337,7 +23337,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H792" t="n">
         <v>11500</v>
@@ -23395,7 +23395,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H794" t="n">
         <v>11000</v>
@@ -23424,7 +23424,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H799" t="n">
         <v>9000</v>
@@ -23569,7 +23569,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H800" t="n">
         <v>1500</v>
@@ -23598,7 +23598,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H801" t="n">
         <v>6000</v>
@@ -23627,7 +23627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H802" t="n">
         <v>15000</v>
@@ -23685,7 +23685,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23714,7 +23714,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H805" t="n">
         <v>5500</v>
@@ -23743,7 +23743,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H806" t="n">
         <v>7500</v>
@@ -23772,7 +23772,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H807" t="n">
         <v>12000</v>
@@ -23801,7 +23801,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H808" t="n">
         <v>5500</v>
@@ -23830,7 +23830,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H810" t="n">
         <v>2500</v>
@@ -23917,7 +23917,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H812" t="n">
         <v>9500</v>
@@ -24091,7 +24091,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H818" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H822" t="n">
         <v>1500</v>
@@ -24236,7 +24236,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H823" t="n">
         <v>500</v>
@@ -24265,7 +24265,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24381,7 +24381,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H828" t="n">
         <v>6000</v>
@@ -24439,7 +24439,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H830" t="n">
         <v>4000</v>
@@ -24584,7 +24584,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475769519806</v>
+        <v>1.57475757598877</v>
       </c>
       <c r="H835" t="n">
         <v>21000</v>
@@ -24613,7 +24613,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.58453869819641</v>
+        <v>1.5845388174057</v>
       </c>
       <c r="H836" t="n">
         <v>4500</v>
@@ -24903,7 +24903,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H846" t="n">
         <v>14000</v>
@@ -24932,7 +24932,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H851" t="n">
         <v>17500</v>
@@ -25077,7 +25077,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H852" t="n">
         <v>92500</v>
@@ -25135,7 +25135,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388194561005</v>
+        <v>1.61388206481934</v>
       </c>
       <c r="H854" t="n">
         <v>9000</v>
@@ -25193,7 +25193,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H856" t="n">
         <v>34000</v>
@@ -25309,7 +25309,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H860" t="n">
         <v>11000</v>
@@ -43266,6 +43266,35 @@
         <v>18000</v>
       </c>
       <c r="I1479" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>1.50999999046326</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="H1480" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1480" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -43298,6 +43298,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1481">
+      <c r="A1481" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>1.53999996185303</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>1.5900000333786</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="H1481" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I1481" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -43327,6 +43327,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1482">
+      <c r="A1482" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1482" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>1.70000004768372</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>1.54999995231628</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1482" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H12" t="n">
         <v>16000</v>
@@ -775,7 +775,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H14" t="n">
         <v>30000</v>
@@ -804,7 +804,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H15" t="n">
         <v>11000</v>
@@ -949,7 +949,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717658996582</v>
+        <v>2.80717635154724</v>
       </c>
       <c r="H20" t="n">
         <v>19000</v>
@@ -1007,7 +1007,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H22" t="n">
         <v>3000</v>
@@ -1065,7 +1065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H24" t="n">
         <v>33000</v>
@@ -1094,7 +1094,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H25" t="n">
         <v>20000</v>
@@ -1210,7 +1210,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H29" t="n">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1326,7 +1326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1471,7 +1471,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H38" t="n">
         <v>3000</v>
@@ -1500,7 +1500,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H39" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H46" t="n">
         <v>13000</v>
@@ -2225,7 +2225,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H64" t="n">
         <v>35000</v>
@@ -2312,7 +2312,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H67" t="n">
         <v>83000</v>
@@ -2370,7 +2370,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2486,7 +2486,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H73" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H77" t="n">
         <v>1000</v>
@@ -2631,7 +2631,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H79" t="n">
         <v>4000</v>
@@ -2863,7 +2863,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2950,7 +2950,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H95" t="n">
         <v>15000</v>
@@ -3153,7 +3153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H100" t="n">
         <v>58000</v>
@@ -3327,7 +3327,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H102" t="n">
         <v>31000</v>
@@ -3385,7 +3385,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H104" t="n">
         <v>7000</v>
@@ -3414,7 +3414,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H105" t="n">
         <v>47000</v>
@@ -3501,7 +3501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H108" t="n">
         <v>46000</v>
@@ -3762,7 +3762,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H117" t="n">
         <v>2000</v>
@@ -3791,7 +3791,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H118" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -3907,7 +3907,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H122" t="n">
         <v>11000</v>
@@ -3936,7 +3936,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H123" t="n">
         <v>12000</v>
@@ -3994,7 +3994,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H125" t="n">
         <v>6500</v>
@@ -4081,7 +4081,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H128" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H139" t="n">
         <v>6500</v>
@@ -4429,7 +4429,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4458,7 +4458,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H141" t="n">
         <v>16500</v>
@@ -4545,7 +4545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H147" t="n">
         <v>2500</v>
@@ -4661,7 +4661,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H148" t="n">
         <v>1500</v>
@@ -4690,7 +4690,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H149" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H152" t="n">
         <v>6500</v>
@@ -4806,7 +4806,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H153" t="n">
         <v>3500</v>
@@ -4835,7 +4835,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H160" t="n">
         <v>2500</v>
@@ -5038,7 +5038,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H161" t="n">
         <v>2000</v>
@@ -5067,7 +5067,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H163" t="n">
         <v>1500</v>
@@ -5125,7 +5125,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5154,7 +5154,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498757362366</v>
+        <v>2.90498781204224</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.91476893424988</v>
+        <v>2.9147686958313</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H174" t="n">
         <v>119000</v>
@@ -5473,7 +5473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H176" t="n">
         <v>17500</v>
@@ -5705,7 +5705,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H184" t="n">
         <v>11000</v>
@@ -5734,7 +5734,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H191" t="n">
         <v>45000</v>
@@ -5937,7 +5937,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H192" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776412963867</v>
+        <v>3.22776389122009</v>
       </c>
       <c r="H198" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.1690776348114</v>
+        <v>3.16907739639282</v>
       </c>
       <c r="H203" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820164680481</v>
+        <v>3.20820188522339</v>
       </c>
       <c r="H205" t="n">
         <v>5500</v>
@@ -6372,7 +6372,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H207" t="n">
         <v>7000</v>
@@ -6401,7 +6401,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H208" t="n">
         <v>12500</v>
@@ -6430,7 +6430,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H209" t="n">
         <v>2500</v>
@@ -6546,7 +6546,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H213" t="n">
         <v>7000</v>
@@ -6575,7 +6575,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H214" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H216" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H219" t="n">
         <v>14000</v>
@@ -6749,7 +6749,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294834136963</v>
+        <v>3.44294810295105</v>
       </c>
       <c r="H220" t="n">
         <v>209000</v>
@@ -6778,7 +6778,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229170799255</v>
+        <v>3.47229146957397</v>
       </c>
       <c r="H221" t="n">
         <v>221000</v>
@@ -6807,7 +6807,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H222" t="n">
         <v>65000</v>
@@ -7039,7 +7039,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H230" t="n">
         <v>25000</v>
@@ -7097,7 +7097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426184654236</v>
+        <v>3.38426160812378</v>
       </c>
       <c r="H233" t="n">
         <v>18000</v>
@@ -7155,7 +7155,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H234" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557511329651</v>
+        <v>3.32557535171509</v>
       </c>
       <c r="H238" t="n">
         <v>8500</v>
@@ -7300,7 +7300,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645038604736</v>
+        <v>3.28645062446594</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7445,7 +7445,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.29623174667358</v>
+        <v>3.296231508255</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7561,7 +7561,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H248" t="n">
         <v>11500</v>
@@ -7648,7 +7648,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H251" t="n">
         <v>25500</v>
@@ -7735,7 +7735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H254" t="n">
         <v>18000</v>
@@ -7764,7 +7764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H256" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.0517041683197</v>
+        <v>3.05170392990112</v>
       </c>
       <c r="H262" t="n">
         <v>11500</v>
@@ -7996,7 +7996,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995314598083</v>
+        <v>3.12995290756226</v>
       </c>
       <c r="H263" t="n">
         <v>11500</v>
@@ -8083,7 +8083,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951515197754</v>
+        <v>3.14951539039612</v>
       </c>
       <c r="H266" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H275" t="n">
         <v>2500</v>
@@ -8373,7 +8373,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279879570007</v>
+        <v>3.00279855728149</v>
       </c>
       <c r="H277" t="n">
         <v>500</v>
@@ -8431,7 +8431,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104753494263</v>
+        <v>3.08104777336121</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257967948914</v>
+        <v>3.01257991790771</v>
       </c>
       <c r="H284" t="n">
         <v>1500</v>
@@ -8634,7 +8634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389294624329</v>
+        <v>2.95389318466187</v>
       </c>
       <c r="H285" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411206245422</v>
+        <v>2.94411182403564</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586308479309</v>
+        <v>2.86586332321167</v>
       </c>
       <c r="H291" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564444541931</v>
+        <v>2.87564420700073</v>
       </c>
       <c r="H298" t="n">
         <v>8500</v>
@@ -9040,7 +9040,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542556762695</v>
+        <v>2.88542532920837</v>
       </c>
       <c r="H299" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9330,7 +9330,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9417,7 +9417,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H313" t="n">
         <v>5500</v>
@@ -9475,7 +9475,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H314" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520645141602</v>
+        <v>2.89520668983459</v>
       </c>
       <c r="H317" t="n">
         <v>14500</v>
@@ -9591,7 +9591,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.8267388343811</v>
+        <v>2.82673907279968</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83651995658875</v>
+        <v>2.83652019500732</v>
       </c>
       <c r="H320" t="n">
         <v>2000</v>
@@ -9736,7 +9736,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H323" t="n">
         <v>500</v>
@@ -9765,7 +9765,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892761230469</v>
+        <v>2.72892785072327</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111686706543</v>
+        <v>2.63111662864685</v>
       </c>
       <c r="H344" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H345" t="n">
         <v>8000</v>
@@ -10461,7 +10461,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -11041,7 +11041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H368" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H369" t="n">
         <v>10000</v>
@@ -11099,7 +11099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H370" t="n">
         <v>5000</v>
@@ -11157,7 +11157,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H372" t="n">
         <v>2500</v>
@@ -11186,7 +11186,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921582221985</v>
+        <v>2.26921606063843</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H376" t="n">
         <v>4000</v>
@@ -11302,7 +11302,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H383" t="n">
         <v>1000</v>
@@ -11505,7 +11505,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H385" t="n">
         <v>2000</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74849009513855</v>
+        <v>2.74848985671997</v>
       </c>
       <c r="H390" t="n">
         <v>40500</v>
@@ -11882,7 +11882,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H397" t="n">
         <v>2500</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H425" t="n">
         <v>1000</v>
@@ -12723,7 +12723,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067887306213</v>
+        <v>2.65067911148071</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H442" t="n">
         <v>500</v>
@@ -13216,7 +13216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H450" t="n">
         <v>5000</v>
@@ -13448,7 +13448,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H458" t="n">
         <v>2000</v>
@@ -13680,7 +13680,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834007263184</v>
+        <v>2.30834031105042</v>
       </c>
       <c r="H459" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H471" t="n">
         <v>5500</v>
@@ -14057,7 +14057,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440003395081</v>
+        <v>2.48440027236938</v>
       </c>
       <c r="H485" t="n">
         <v>3000</v>
@@ -14724,7 +14724,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H519" t="n">
         <v>2000</v>
@@ -15536,7 +15536,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H523" t="n">
         <v>1500</v>
@@ -15565,7 +15565,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658928871155</v>
+        <v>2.38658905029297</v>
       </c>
       <c r="H535" t="n">
         <v>56000</v>
@@ -15942,7 +15942,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768367767334</v>
+        <v>2.33768391609192</v>
       </c>
       <c r="H537" t="n">
         <v>11000</v>
@@ -16000,7 +16000,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H539" t="n">
         <v>18500</v>
@@ -16058,7 +16058,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H541" t="n">
         <v>5500</v>
@@ -16087,7 +16087,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593265533447</v>
+        <v>2.41593241691589</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H545" t="n">
         <v>4000</v>
@@ -16377,7 +16377,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16667,7 +16667,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461891174316</v>
+        <v>2.47461915016174</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16812,7 +16812,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H568" t="n">
         <v>2500</v>
@@ -16870,7 +16870,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H569" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418139457703</v>
+        <v>2.49418115615845</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637017250061</v>
+        <v>2.39637041091919</v>
       </c>
       <c r="H573" t="n">
         <v>12000</v>
@@ -17218,7 +17218,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009133338928</v>
+        <v>2.23009157180786</v>
       </c>
       <c r="H581" t="n">
         <v>500</v>
@@ -17305,7 +17305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H584" t="n">
         <v>2000</v>
@@ -17334,7 +17334,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H588" t="n">
         <v>2500</v>
@@ -17450,7 +17450,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.32790279388428</v>
+        <v>2.3279025554657</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H591" t="n">
         <v>1000</v>
@@ -17537,7 +17537,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965381622314</v>
+        <v>2.24965357780457</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H603" t="n">
         <v>1000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H604" t="n">
         <v>3500</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H607" t="n">
         <v>2500</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H611" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H612" t="n">
         <v>2000</v>
@@ -18146,7 +18146,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H616" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H617" t="n">
         <v>500</v>
@@ -18378,7 +18378,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016090393066</v>
+        <v>1.78016078472137</v>
       </c>
       <c r="H621" t="n">
         <v>32500</v>
@@ -18465,7 +18465,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H624" t="n">
         <v>11000</v>
@@ -18552,7 +18552,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H627" t="n">
         <v>6500</v>
@@ -18581,7 +18581,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H628" t="n">
         <v>10000</v>
@@ -18755,7 +18755,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H634" t="n">
         <v>2500</v>
@@ -18784,7 +18784,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H655" t="n">
         <v>17000</v>
@@ -19393,7 +19393,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H656" t="n">
         <v>20000</v>
@@ -19422,7 +19422,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H660" t="n">
         <v>32000</v>
@@ -19538,7 +19538,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H661" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19712,7 +19712,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H667" t="n">
         <v>2000</v>
@@ -19741,7 +19741,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H672" t="n">
         <v>500</v>
@@ -19915,7 +19915,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H674" t="n">
         <v>4000</v>
@@ -20176,7 +20176,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037954330444</v>
+        <v>1.77037966251373</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20379,7 +20379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H690" t="n">
         <v>13500</v>
@@ -20408,7 +20408,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840952396393</v>
+        <v>1.85840964317322</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H701" t="n">
         <v>7000</v>
@@ -20756,7 +20756,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.07359385490417</v>
+        <v>2.0735936164856</v>
       </c>
       <c r="H703" t="n">
         <v>500</v>
@@ -20843,7 +20843,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20959,7 +20959,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096732139587</v>
+        <v>2.19096708297729</v>
       </c>
       <c r="H710" t="n">
         <v>1000</v>
@@ -21017,7 +21017,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H712" t="n">
         <v>3500</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315609931946</v>
+        <v>2.09315633773804</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534511566162</v>
+        <v>1.99534499645233</v>
       </c>
       <c r="H716" t="n">
         <v>500</v>
@@ -21220,7 +21220,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H719" t="n">
         <v>6500</v>
@@ -21249,7 +21249,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797176837921</v>
+        <v>1.87797164916992</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147417068481</v>
+        <v>1.72147405147552</v>
       </c>
       <c r="H722" t="n">
         <v>5500</v>
@@ -21336,7 +21336,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.6530065536499</v>
+        <v>1.65300643444061</v>
       </c>
       <c r="H723" t="n">
         <v>9500</v>
@@ -21655,7 +21655,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395139694214</v>
+        <v>1.16395127773285</v>
       </c>
       <c r="H734" t="n">
         <v>68000</v>
@@ -21742,7 +21742,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H737" t="n">
         <v>54000</v>
@@ -21800,7 +21800,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657804965973</v>
+        <v>1.04657816886902</v>
       </c>
       <c r="H739" t="n">
         <v>56500</v>
@@ -21829,7 +21829,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329464435577</v>
+        <v>1.19329452514648</v>
       </c>
       <c r="H740" t="n">
         <v>95000</v>
@@ -21916,7 +21916,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H743" t="n">
         <v>31000</v>
@@ -21945,7 +21945,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H744" t="n">
         <v>20000</v>
@@ -21974,7 +21974,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22177,7 +22177,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044887542725</v>
+        <v>1.32044899463654</v>
       </c>
       <c r="H752" t="n">
         <v>18500</v>
@@ -22554,7 +22554,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H765" t="n">
         <v>24000</v>
@@ -22612,7 +22612,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H767" t="n">
         <v>7500</v>
@@ -22670,7 +22670,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H769" t="n">
         <v>4000</v>
@@ -22699,7 +22699,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H770" t="n">
         <v>8000</v>
@@ -23047,7 +23047,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.6041008234024</v>
+        <v>1.60410094261169</v>
       </c>
       <c r="H782" t="n">
         <v>108000</v>
@@ -23105,7 +23105,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H784" t="n">
         <v>9500</v>
@@ -23163,7 +23163,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H786" t="n">
         <v>8500</v>
@@ -23192,7 +23192,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H787" t="n">
         <v>10500</v>
@@ -23221,7 +23221,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H788" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H790" t="n">
         <v>3500</v>
@@ -23308,7 +23308,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H791" t="n">
         <v>5000</v>
@@ -23337,7 +23337,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H792" t="n">
         <v>11500</v>
@@ -23395,7 +23395,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H794" t="n">
         <v>11000</v>
@@ -23424,7 +23424,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H799" t="n">
         <v>9000</v>
@@ -23569,7 +23569,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H800" t="n">
         <v>1500</v>
@@ -23598,7 +23598,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H801" t="n">
         <v>6000</v>
@@ -23627,7 +23627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H802" t="n">
         <v>15000</v>
@@ -23685,7 +23685,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23714,7 +23714,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H805" t="n">
         <v>5500</v>
@@ -23743,7 +23743,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H806" t="n">
         <v>7500</v>
@@ -23772,7 +23772,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H807" t="n">
         <v>12000</v>
@@ -23801,7 +23801,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H808" t="n">
         <v>5500</v>
@@ -23830,7 +23830,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H810" t="n">
         <v>2500</v>
@@ -23917,7 +23917,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41825997829437</v>
+        <v>1.41826009750366</v>
       </c>
       <c r="H812" t="n">
         <v>9500</v>
@@ -24091,7 +24091,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782222270966</v>
+        <v>1.43782210350037</v>
       </c>
       <c r="H818" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H822" t="n">
         <v>1500</v>
@@ -24236,7 +24236,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H823" t="n">
         <v>500</v>
@@ -24265,7 +24265,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24381,7 +24381,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738446712494</v>
+        <v>1.45738434791565</v>
       </c>
       <c r="H828" t="n">
         <v>6000</v>
@@ -24439,7 +24439,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.44760322570801</v>
+        <v>1.4476033449173</v>
       </c>
       <c r="H830" t="n">
         <v>4000</v>
@@ -24584,7 +24584,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475757598877</v>
+        <v>1.57475769519806</v>
       </c>
       <c r="H835" t="n">
         <v>21000</v>
@@ -24613,7 +24613,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.5845388174057</v>
+        <v>1.58453869819641</v>
       </c>
       <c r="H836" t="n">
         <v>4500</v>
@@ -24903,7 +24903,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H846" t="n">
         <v>14000</v>
@@ -24932,7 +24932,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694647312164</v>
+        <v>1.47694659233093</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628983974457</v>
+        <v>1.50628995895386</v>
       </c>
       <c r="H851" t="n">
         <v>17500</v>
@@ -25077,7 +25077,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322519302368</v>
+        <v>1.64322531223297</v>
       </c>
       <c r="H852" t="n">
         <v>92500</v>
@@ -25135,7 +25135,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388206481934</v>
+        <v>1.61388194561005</v>
       </c>
       <c r="H854" t="n">
         <v>9000</v>
@@ -25193,7 +25193,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278755664825</v>
+        <v>1.66278767585754</v>
       </c>
       <c r="H856" t="n">
         <v>34000</v>
@@ -25309,7 +25309,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125517368317</v>
+        <v>1.73125529289246</v>
       </c>
       <c r="H860" t="n">
         <v>11000</v>
@@ -43353,6 +43353,35 @@
         <v>13000</v>
       </c>
       <c r="I1482" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1483" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="D1483" t="n">
+        <v>1.6599999666214</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>1.55999994277954</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="G1483" t="n">
+        <v>1.63999998569489</v>
+      </c>
+      <c r="H1483" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1483" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CVG.MI.xlsx
+++ b/data/CVG.MI.xlsx
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H9" t="n">
         <v>6000</v>
@@ -717,7 +717,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G12" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H12" t="n">
         <v>16000</v>
@@ -775,7 +775,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G14" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H14" t="n">
         <v>30000</v>
@@ -804,7 +804,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H15" t="n">
         <v>11000</v>
@@ -949,7 +949,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>2.80717635154724</v>
+        <v>2.80717658996582</v>
       </c>
       <c r="H20" t="n">
         <v>19000</v>
@@ -1007,7 +1007,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G22" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H22" t="n">
         <v>3000</v>
@@ -1065,7 +1065,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G24" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H24" t="n">
         <v>33000</v>
@@ -1094,7 +1094,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H25" t="n">
         <v>20000</v>
@@ -1210,7 +1210,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H29" t="n">
         <v>1000</v>
@@ -1297,7 +1297,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G32" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1326,7 +1326,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G33" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H33" t="n">
         <v>9000</v>
@@ -1471,7 +1471,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H38" t="n">
         <v>3000</v>
@@ -1500,7 +1500,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H39" t="n">
         <v>7000</v>
@@ -1674,7 +1674,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H45" t="n">
         <v>25000</v>
@@ -1703,7 +1703,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H46" t="n">
         <v>13000</v>
@@ -2225,7 +2225,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G64" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H64" t="n">
         <v>35000</v>
@@ -2312,7 +2312,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G67" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H67" t="n">
         <v>83000</v>
@@ -2370,7 +2370,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2486,7 +2486,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G73" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H73" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G77" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H77" t="n">
         <v>1000</v>
@@ -2631,7 +2631,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G78" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H79" t="n">
         <v>4000</v>
@@ -2863,7 +2863,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H86" t="n">
         <v>4000</v>
@@ -2950,7 +2950,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3124,7 +3124,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G95" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H95" t="n">
         <v>15000</v>
@@ -3153,7 +3153,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G96" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G100" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H100" t="n">
         <v>58000</v>
@@ -3327,7 +3327,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G102" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H102" t="n">
         <v>31000</v>
@@ -3385,7 +3385,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H104" t="n">
         <v>7000</v>
@@ -3414,7 +3414,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H105" t="n">
         <v>47000</v>
@@ -3501,7 +3501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H108" t="n">
         <v>46000</v>
@@ -3762,7 +3762,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G117" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H117" t="n">
         <v>2000</v>
@@ -3791,7 +3791,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G118" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H118" t="n">
         <v>5000</v>
@@ -3878,7 +3878,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H121" t="n">
         <v>1000</v>
@@ -3907,7 +3907,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H122" t="n">
         <v>11000</v>
@@ -3936,7 +3936,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H123" t="n">
         <v>12000</v>
@@ -3994,7 +3994,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G125" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H125" t="n">
         <v>6500</v>
@@ -4081,7 +4081,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H128" t="n">
         <v>5500</v>
@@ -4284,7 +4284,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H135" t="n">
         <v>1000</v>
@@ -4313,7 +4313,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G136" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H139" t="n">
         <v>6500</v>
@@ -4429,7 +4429,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H140" t="n">
         <v>10000</v>
@@ -4458,7 +4458,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G141" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H141" t="n">
         <v>16500</v>
@@ -4545,7 +4545,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H144" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G147" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H147" t="n">
         <v>2500</v>
@@ -4661,7 +4661,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G148" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H148" t="n">
         <v>1500</v>
@@ -4690,7 +4690,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G149" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H149" t="n">
         <v>2500</v>
@@ -4777,7 +4777,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G152" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H152" t="n">
         <v>6500</v>
@@ -4806,7 +4806,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H153" t="n">
         <v>3500</v>
@@ -4835,7 +4835,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G154" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H154" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G155" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G160" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H160" t="n">
         <v>2500</v>
@@ -5038,7 +5038,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G161" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H161" t="n">
         <v>2000</v>
@@ -5067,7 +5067,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G163" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H163" t="n">
         <v>1500</v>
@@ -5125,7 +5125,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H164" t="n">
         <v>6000</v>
@@ -5154,7 +5154,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G165" t="n">
-        <v>2.90498781204224</v>
+        <v>2.90498757362366</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G166" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H166" t="n">
         <v>2500</v>
@@ -5212,7 +5212,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>2.9147686958313</v>
+        <v>2.91476893424988</v>
       </c>
       <c r="H167" t="n">
         <v>2000</v>
@@ -5241,7 +5241,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G168" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H168" t="n">
         <v>500</v>
@@ -5386,7 +5386,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G173" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H173" t="n">
         <v>72000</v>
@@ -5415,7 +5415,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G174" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H174" t="n">
         <v>119000</v>
@@ -5473,7 +5473,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H176" t="n">
         <v>17500</v>
@@ -5705,7 +5705,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G184" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H184" t="n">
         <v>11000</v>
@@ -5734,7 +5734,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G185" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G186" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H186" t="n">
         <v>500</v>
@@ -5821,7 +5821,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H188" t="n">
         <v>4000</v>
@@ -5908,7 +5908,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H191" t="n">
         <v>45000</v>
@@ -5937,7 +5937,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G192" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H192" t="n">
         <v>5000</v>
@@ -5966,7 +5966,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G198" t="n">
-        <v>3.22776389122009</v>
+        <v>3.22776412963867</v>
       </c>
       <c r="H198" t="n">
         <v>20500</v>
@@ -6256,7 +6256,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>3.16907739639282</v>
+        <v>3.1690776348114</v>
       </c>
       <c r="H203" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G205" t="n">
-        <v>3.20820188522339</v>
+        <v>3.20820164680481</v>
       </c>
       <c r="H205" t="n">
         <v>5500</v>
@@ -6372,7 +6372,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G207" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H207" t="n">
         <v>7000</v>
@@ -6401,7 +6401,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G208" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H208" t="n">
         <v>12500</v>
@@ -6430,7 +6430,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G209" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H209" t="n">
         <v>2500</v>
@@ -6546,7 +6546,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G213" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H213" t="n">
         <v>7000</v>
@@ -6575,7 +6575,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G214" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H214" t="n">
         <v>5000</v>
@@ -6633,7 +6633,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G216" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H216" t="n">
         <v>4000</v>
@@ -6720,7 +6720,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G219" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H219" t="n">
         <v>14000</v>
@@ -6749,7 +6749,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G220" t="n">
-        <v>3.44294810295105</v>
+        <v>3.44294834136963</v>
       </c>
       <c r="H220" t="n">
         <v>209000</v>
@@ -6778,7 +6778,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>3.47229146957397</v>
+        <v>3.47229170799255</v>
       </c>
       <c r="H221" t="n">
         <v>221000</v>
@@ -6807,7 +6807,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G222" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H222" t="n">
         <v>65000</v>
@@ -7039,7 +7039,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H230" t="n">
         <v>25000</v>
@@ -7097,7 +7097,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H232" t="n">
         <v>5000</v>
@@ -7126,7 +7126,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>3.38426160812378</v>
+        <v>3.38426184654236</v>
       </c>
       <c r="H233" t="n">
         <v>18000</v>
@@ -7155,7 +7155,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G234" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H234" t="n">
         <v>10000</v>
@@ -7271,7 +7271,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>3.32557535171509</v>
+        <v>3.32557511329651</v>
       </c>
       <c r="H238" t="n">
         <v>8500</v>
@@ -7300,7 +7300,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G239" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G240" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G241" t="n">
-        <v>3.28645062446594</v>
+        <v>3.28645038604736</v>
       </c>
       <c r="H241" t="n">
         <v>2500</v>
@@ -7445,7 +7445,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G244" t="n">
-        <v>3.296231508255</v>
+        <v>3.29623174667358</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7561,7 +7561,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G248" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H248" t="n">
         <v>11500</v>
@@ -7648,7 +7648,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H251" t="n">
         <v>25500</v>
@@ -7735,7 +7735,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G254" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H254" t="n">
         <v>18000</v>
@@ -7764,7 +7764,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G256" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H256" t="n">
         <v>2500</v>
@@ -7967,7 +7967,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G262" t="n">
-        <v>3.05170392990112</v>
+        <v>3.0517041683197</v>
       </c>
       <c r="H262" t="n">
         <v>11500</v>
@@ -7996,7 +7996,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G263" t="n">
-        <v>3.12995290756226</v>
+        <v>3.12995314598083</v>
       </c>
       <c r="H263" t="n">
         <v>11500</v>
@@ -8083,7 +8083,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G266" t="n">
-        <v>3.14951539039612</v>
+        <v>3.14951515197754</v>
       </c>
       <c r="H266" t="n">
         <v>1500</v>
@@ -8315,7 +8315,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H274" t="n">
         <v>3000</v>
@@ -8344,7 +8344,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G275" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H275" t="n">
         <v>2500</v>
@@ -8373,7 +8373,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G276" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G277" t="n">
-        <v>3.00279855728149</v>
+        <v>3.00279879570007</v>
       </c>
       <c r="H277" t="n">
         <v>500</v>
@@ -8431,7 +8431,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G278" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H278" t="n">
         <v>500</v>
@@ -8460,7 +8460,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G279" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>3.08104777336121</v>
+        <v>3.08104753494263</v>
       </c>
       <c r="H283" t="n">
         <v>1500</v>
@@ -8605,7 +8605,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>3.01257991790771</v>
+        <v>3.01257967948914</v>
       </c>
       <c r="H284" t="n">
         <v>1500</v>
@@ -8634,7 +8634,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G285" t="n">
-        <v>2.95389318466187</v>
+        <v>2.95389294624329</v>
       </c>
       <c r="H285" t="n">
         <v>5000</v>
@@ -8721,7 +8721,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G288" t="n">
-        <v>2.94411182403564</v>
+        <v>2.94411206245422</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G289" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H289" t="n">
         <v>2000</v>
@@ -8779,7 +8779,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G290" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H290" t="n">
         <v>3000</v>
@@ -8808,7 +8808,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G291" t="n">
-        <v>2.86586332321167</v>
+        <v>2.86586308479309</v>
       </c>
       <c r="H291" t="n">
         <v>6000</v>
@@ -9011,7 +9011,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G298" t="n">
-        <v>2.87564420700073</v>
+        <v>2.87564444541931</v>
       </c>
       <c r="H298" t="n">
         <v>8500</v>
@@ -9040,7 +9040,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G299" t="n">
-        <v>2.88542532920837</v>
+        <v>2.88542556762695</v>
       </c>
       <c r="H299" t="n">
         <v>2000</v>
@@ -9185,7 +9185,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G304" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H304" t="n">
         <v>1500</v>
@@ -9330,7 +9330,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H309" t="n">
         <v>1000</v>
@@ -9359,7 +9359,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G310" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G311" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H311" t="n">
         <v>5000</v>
@@ -9417,7 +9417,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G312" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H312" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G313" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H313" t="n">
         <v>5500</v>
@@ -9475,7 +9475,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H314" t="n">
         <v>500</v>
@@ -9562,7 +9562,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>2.89520668983459</v>
+        <v>2.89520645141602</v>
       </c>
       <c r="H317" t="n">
         <v>14500</v>
@@ -9591,7 +9591,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G318" t="n">
-        <v>2.82673907279968</v>
+        <v>2.8267388343811</v>
       </c>
       <c r="H318" t="n">
         <v>5000</v>
@@ -9649,7 +9649,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>2.83652019500732</v>
+        <v>2.83651995658875</v>
       </c>
       <c r="H320" t="n">
         <v>2000</v>
@@ -9736,7 +9736,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G323" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H323" t="n">
         <v>500</v>
@@ -9765,7 +9765,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G326" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H326" t="n">
         <v>1500</v>
@@ -9852,7 +9852,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G327" t="n">
-        <v>2.72892785072327</v>
+        <v>2.72892761230469</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G344" t="n">
-        <v>2.63111662864685</v>
+        <v>2.63111686706543</v>
       </c>
       <c r="H344" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G345" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H345" t="n">
         <v>8000</v>
@@ -10461,7 +10461,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G348" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H348" t="n">
         <v>500</v>
@@ -11041,7 +11041,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G368" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H368" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G369" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H369" t="n">
         <v>10000</v>
@@ -11099,7 +11099,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G370" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H370" t="n">
         <v>5000</v>
@@ -11157,7 +11157,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H372" t="n">
         <v>2500</v>
@@ -11186,7 +11186,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G373" t="n">
-        <v>2.26921606063843</v>
+        <v>2.26921582221985</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H376" t="n">
         <v>4000</v>
@@ -11302,7 +11302,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H383" t="n">
         <v>1000</v>
@@ -11505,7 +11505,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G384" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G385" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H385" t="n">
         <v>2000</v>
@@ -11679,7 +11679,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G390" t="n">
-        <v>2.74848985671997</v>
+        <v>2.74849009513855</v>
       </c>
       <c r="H390" t="n">
         <v>40500</v>
@@ -11882,7 +11882,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G397" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H397" t="n">
         <v>2500</v>
@@ -11911,7 +11911,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G398" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H398" t="n">
         <v>500</v>
@@ -12694,7 +12694,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H425" t="n">
         <v>1000</v>
@@ -12723,7 +12723,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>2.65067911148071</v>
+        <v>2.65067887306213</v>
       </c>
       <c r="H426" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G442" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H442" t="n">
         <v>500</v>
@@ -13216,7 +13216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G443" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H443" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G444" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H444" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G446" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H446" t="n">
         <v>1000</v>
@@ -13332,7 +13332,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H447" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G449" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H449" t="n">
         <v>2500</v>
@@ -13419,7 +13419,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G450" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H450" t="n">
         <v>5000</v>
@@ -13448,7 +13448,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G451" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13651,7 +13651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G458" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H458" t="n">
         <v>2000</v>
@@ -13680,7 +13680,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G459" t="n">
-        <v>2.30834031105042</v>
+        <v>2.30834007263184</v>
       </c>
       <c r="H459" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G471" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H471" t="n">
         <v>5500</v>
@@ -14057,7 +14057,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G472" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H472" t="n">
         <v>4500</v>
@@ -14434,7 +14434,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G485" t="n">
-        <v>2.48440027236938</v>
+        <v>2.48440003395081</v>
       </c>
       <c r="H485" t="n">
         <v>3000</v>
@@ -14724,7 +14724,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G495" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H495" t="n">
         <v>500</v>
@@ -14811,7 +14811,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G498" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H498" t="n">
         <v>1500</v>
@@ -14840,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G499" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G500" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G501" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G502" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G503" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G504" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G505" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H505" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G506" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G507" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G508" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G509" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G519" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H519" t="n">
         <v>2000</v>
@@ -15536,7 +15536,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G523" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H523" t="n">
         <v>1500</v>
@@ -15565,7 +15565,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G524" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.38658905029297</v>
+        <v>2.38658928871155</v>
       </c>
       <c r="H535" t="n">
         <v>56000</v>
@@ -15942,7 +15942,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G537" t="n">
-        <v>2.33768391609192</v>
+        <v>2.33768367767334</v>
       </c>
       <c r="H537" t="n">
         <v>11000</v>
@@ -16000,7 +16000,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G539" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H539" t="n">
         <v>18500</v>
@@ -16058,7 +16058,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G541" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H541" t="n">
         <v>5500</v>
@@ -16087,7 +16087,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G542" t="n">
-        <v>2.41593241691589</v>
+        <v>2.41593265533447</v>
       </c>
       <c r="H542" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G545" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H545" t="n">
         <v>4000</v>
@@ -16377,7 +16377,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G552" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H552" t="n">
         <v>500</v>
@@ -16667,7 +16667,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G562" t="n">
-        <v>2.47461915016174</v>
+        <v>2.47461891174316</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16783,7 +16783,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G566" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H566" t="n">
         <v>500</v>
@@ -16812,7 +16812,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G567" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G568" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H568" t="n">
         <v>2500</v>
@@ -16870,7 +16870,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G569" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H569" t="n">
         <v>1500</v>
@@ -16899,7 +16899,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G570" t="n">
-        <v>2.49418115615845</v>
+        <v>2.49418139457703</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G573" t="n">
-        <v>2.39637041091919</v>
+        <v>2.39637017250061</v>
       </c>
       <c r="H573" t="n">
         <v>12000</v>
@@ -17218,7 +17218,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G581" t="n">
-        <v>2.23009157180786</v>
+        <v>2.23009133338928</v>
       </c>
       <c r="H581" t="n">
         <v>500</v>
@@ -17305,7 +17305,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G584" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H584" t="n">
         <v>2000</v>
@@ -17334,7 +17334,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G585" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H585" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G586" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H586" t="n">
         <v>0</v>
@@ -17392,7 +17392,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G587" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H587" t="n">
         <v>1500</v>
@@ -17421,7 +17421,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H588" t="n">
         <v>2500</v>
@@ -17450,7 +17450,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G589" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H589" t="n">
         <v>0</v>
@@ -17479,7 +17479,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G590" t="n">
-        <v>2.3279025554657</v>
+        <v>2.32790279388428</v>
       </c>
       <c r="H590" t="n">
         <v>0</v>
@@ -17508,7 +17508,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G591" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H591" t="n">
         <v>1000</v>
@@ -17537,7 +17537,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G592" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H592" t="n">
         <v>0</v>
@@ -17566,7 +17566,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G593" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G594" t="n">
-        <v>2.24965357780457</v>
+        <v>2.24965381622314</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G601" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H601" t="n">
         <v>500</v>
@@ -17827,7 +17827,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G602" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G603" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H603" t="n">
         <v>1000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H604" t="n">
         <v>3500</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H607" t="n">
         <v>2500</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H611" t="n">
         <v>2000</v>
@@ -18117,7 +18117,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G612" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H612" t="n">
         <v>2000</v>
@@ -18146,7 +18146,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G613" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G616" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H616" t="n">
         <v>1500</v>
@@ -18262,7 +18262,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G617" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H617" t="n">
         <v>500</v>
@@ -18378,7 +18378,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G621" t="n">
-        <v>1.78016078472137</v>
+        <v>1.78016090393066</v>
       </c>
       <c r="H621" t="n">
         <v>32500</v>
@@ -18465,7 +18465,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G624" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H624" t="n">
         <v>11000</v>
@@ -18552,7 +18552,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H627" t="n">
         <v>6500</v>
@@ -18581,7 +18581,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G628" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H628" t="n">
         <v>10000</v>
@@ -18755,7 +18755,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G634" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H634" t="n">
         <v>2500</v>
@@ -18784,7 +18784,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G635" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G636" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H636" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G655" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H655" t="n">
         <v>17000</v>
@@ -19393,7 +19393,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G656" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H656" t="n">
         <v>20000</v>
@@ -19422,7 +19422,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19509,7 +19509,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G660" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H660" t="n">
         <v>32000</v>
@@ -19538,7 +19538,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G661" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H661" t="n">
         <v>500</v>
@@ -19567,7 +19567,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G662" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H662" t="n">
         <v>1500</v>
@@ -19712,7 +19712,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G667" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H667" t="n">
         <v>2000</v>
@@ -19741,7 +19741,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19770,7 +19770,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G672" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H672" t="n">
         <v>500</v>
@@ -19915,7 +19915,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H674" t="n">
         <v>4000</v>
@@ -20176,7 +20176,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G683" t="n">
-        <v>1.77037966251373</v>
+        <v>1.77037954330444</v>
       </c>
       <c r="H683" t="n">
         <v>1500</v>
@@ -20379,7 +20379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G690" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H690" t="n">
         <v>13500</v>
@@ -20408,7 +20408,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G691" t="n">
-        <v>1.85840964317322</v>
+        <v>1.85840952396393</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G701" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H701" t="n">
         <v>7000</v>
@@ -20756,7 +20756,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G703" t="n">
-        <v>2.0735936164856</v>
+        <v>2.07359385490417</v>
       </c>
       <c r="H703" t="n">
         <v>500</v>
@@ -20843,7 +20843,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G706" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H706" t="n">
         <v>500</v>
@@ -20959,7 +20959,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G710" t="n">
-        <v>2.19096708297729</v>
+        <v>2.19096732139587</v>
       </c>
       <c r="H710" t="n">
         <v>1000</v>
@@ -21017,7 +21017,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G712" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H712" t="n">
         <v>3500</v>
@@ -21046,7 +21046,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G713" t="n">
-        <v>2.09315633773804</v>
+        <v>2.09315609931946</v>
       </c>
       <c r="H713" t="n">
         <v>0</v>
@@ -21133,7 +21133,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G716" t="n">
-        <v>1.99534499645233</v>
+        <v>1.99534511566162</v>
       </c>
       <c r="H716" t="n">
         <v>500</v>
@@ -21220,7 +21220,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G719" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H719" t="n">
         <v>6500</v>
@@ -21249,7 +21249,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G720" t="n">
-        <v>1.87797164916992</v>
+        <v>1.87797176837921</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G722" t="n">
-        <v>1.72147405147552</v>
+        <v>1.72147417068481</v>
       </c>
       <c r="H722" t="n">
         <v>5500</v>
@@ -21336,7 +21336,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.65300643444061</v>
+        <v>1.6530065536499</v>
       </c>
       <c r="H723" t="n">
         <v>9500</v>
@@ -21655,7 +21655,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G734" t="n">
-        <v>1.16395127773285</v>
+        <v>1.16395139694214</v>
       </c>
       <c r="H734" t="n">
         <v>68000</v>
@@ -21742,7 +21742,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G737" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H737" t="n">
         <v>54000</v>
@@ -21800,7 +21800,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G739" t="n">
-        <v>1.04657816886902</v>
+        <v>1.04657804965973</v>
       </c>
       <c r="H739" t="n">
         <v>56500</v>
@@ -21829,7 +21829,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G740" t="n">
-        <v>1.19329452514648</v>
+        <v>1.19329464435577</v>
       </c>
       <c r="H740" t="n">
         <v>95000</v>
@@ -21916,7 +21916,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G743" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H743" t="n">
         <v>31000</v>
@@ -21945,7 +21945,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H744" t="n">
         <v>20000</v>
@@ -21974,7 +21974,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G745" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H745" t="n">
         <v>12000</v>
@@ -22177,7 +22177,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G752" t="n">
-        <v>1.32044899463654</v>
+        <v>1.32044887542725</v>
       </c>
       <c r="H752" t="n">
         <v>18500</v>
@@ -22554,7 +22554,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G765" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H765" t="n">
         <v>24000</v>
@@ -22612,7 +22612,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G767" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H767" t="n">
         <v>7500</v>
@@ -22670,7 +22670,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H769" t="n">
         <v>4000</v>
@@ -22699,7 +22699,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G770" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H770" t="n">
         <v>8000</v>
@@ -23047,7 +23047,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G782" t="n">
-        <v>1.60410094261169</v>
+        <v>1.6041008234024</v>
       </c>
       <c r="H782" t="n">
         <v>108000</v>
@@ -23105,7 +23105,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G784" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H784" t="n">
         <v>9500</v>
@@ -23163,7 +23163,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H786" t="n">
         <v>8500</v>
@@ -23192,7 +23192,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G787" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H787" t="n">
         <v>10500</v>
@@ -23221,7 +23221,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G788" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H788" t="n">
         <v>6000</v>
@@ -23279,7 +23279,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G790" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H790" t="n">
         <v>3500</v>
@@ -23308,7 +23308,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H791" t="n">
         <v>5000</v>
@@ -23337,7 +23337,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H792" t="n">
         <v>11500</v>
@@ -23395,7 +23395,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G794" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H794" t="n">
         <v>11000</v>
@@ -23424,7 +23424,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G795" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -23540,7 +23540,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H799" t="n">
         <v>9000</v>
@@ -23569,7 +23569,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H800" t="n">
         <v>1500</v>
@@ -23598,7 +23598,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G801" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H801" t="n">
         <v>6000</v>
@@ -23627,7 +23627,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G802" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H802" t="n">
         <v>15000</v>
@@ -23685,7 +23685,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G804" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H804" t="n">
         <v>1500</v>
@@ -23714,7 +23714,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G805" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H805" t="n">
         <v>5500</v>
@@ -23743,7 +23743,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H806" t="n">
         <v>7500</v>
@@ -23772,7 +23772,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G807" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H807" t="n">
         <v>12000</v>
@@ -23801,7 +23801,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H808" t="n">
         <v>5500</v>
@@ -23830,7 +23830,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G809" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G810" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H810" t="n">
         <v>2500</v>
@@ -23917,7 +23917,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G812" t="n">
-        <v>1.41826009750366</v>
+        <v>1.41825997829437</v>
       </c>
       <c r="H812" t="n">
         <v>9500</v>
@@ -24091,7 +24091,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G818" t="n">
-        <v>1.43782210350037</v>
+        <v>1.43782222270966</v>
       </c>
       <c r="H818" t="n">
         <v>8000</v>
@@ -24178,7 +24178,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G821" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H821" t="n">
         <v>2000</v>
@@ -24207,7 +24207,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G822" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H822" t="n">
         <v>1500</v>
@@ -24236,7 +24236,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G823" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H823" t="n">
         <v>500</v>
@@ -24265,7 +24265,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H824" t="n">
         <v>1000</v>
@@ -24381,7 +24381,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G828" t="n">
-        <v>1.45738434791565</v>
+        <v>1.45738446712494</v>
       </c>
       <c r="H828" t="n">
         <v>6000</v>
@@ -24439,7 +24439,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.4476033449173</v>
+        <v>1.44760322570801</v>
       </c>
       <c r="H830" t="n">
         <v>4000</v>
@@ -24584,7 +24584,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G835" t="n">
-        <v>1.57475769519806</v>
+        <v>1.57475757598877</v>
       </c>
       <c r="H835" t="n">
         <v>21000</v>
@@ -24613,7 +24613,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G836" t="n">
-        <v>1.58453869819641</v>
+        <v>1.5845388174057</v>
       </c>
       <c r="H836" t="n">
         <v>4500</v>
@@ -24903,7 +24903,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G846" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H846" t="n">
         <v>14000</v>
@@ -24932,7 +24932,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>1.47694659233093</v>
+        <v>1.47694647312164</v>
       </c>
       <c r="H847" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G851" t="n">
-        <v>1.50628995895386</v>
+        <v>1.50628983974457</v>
       </c>
       <c r="H851" t="n">
         <v>17500</v>
@@ -25077,7 +25077,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G852" t="n">
-        <v>1.64322531223297</v>
+        <v>1.64322519302368</v>
       </c>
       <c r="H852" t="n">
         <v>92500</v>
@@ -25135,7 +25135,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G854" t="n">
-        <v>1.61388194561005</v>
+        <v>1.61388206481934</v>
       </c>
       <c r="H854" t="n">
         <v>9000</v>
@@ -25193,7 +25193,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G856" t="n">
-        <v>1.66278767585754</v>
+        <v>1.66278755664825</v>
       </c>
       <c r="H856" t="n">
         <v>34000</v>
@@ -25309,7 +25309,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>1.73125529289246</v>
+        <v>1.73125517368317</v>
       </c>
       <c r="H860" t="n">
         <v>11000</v>
@@ -43382,6 +43382,35 @@
         <v>10500</v>
       </c>
       <c r="I1483" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1484" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="D1484" t="n">
+        <v>1.61000001430511</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>1.58000004291534</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="G1484" t="n">
+        <v>1.60000002384186</v>
+      </c>
+      <c r="H1484" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I1484" t="s">
         <v>9</v>
       </c>
     </row>
